--- a/out/CTBC_VCF911_每步Checklist.xlsx
+++ b/out/CTBC_VCF911_每步Checklist.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2674" uniqueCount="1127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2678" uniqueCount="1130">
   <si>
     <r>
       <rPr>
@@ -2080,7 +2080,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">G5 ⚠ PONR</t>
+    <t xml:space="preserve">G5</t>
   </si>
   <si>
     <r>
@@ -2100,26 +2100,26 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">｜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">vSAN on-disk format</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">｜放行條件：觀察期無重大事件、客戶簽核｜簽核：</t>
+      <t xml:space="preserve">｜結案｜放行條件：觀察期無重大事件、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">As-Built </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">交付、客戶簽核｜簽核：</t>
     </r>
     <r>
       <rPr>
@@ -3358,34 +3358,7 @@
     <t xml:space="preserve">S16</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">觀察期、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">vSAN on-disk format </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">與收尾（新增）</t>
-    </r>
+    <t xml:space="preserve">觀察期與收尾（新增）</t>
   </si>
   <si>
     <t xml:space="preserve">收尾</t>
@@ -21569,17 +21542,161 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">本步不升（留到觀察期後，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">S16</t>
+      <t xml:space="preserve">本案不升（客戶決定）：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ESX </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">升級後不執行 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">vSphere Client &gt; vSAN &gt; Disk Management &gt; Upgrade</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TechDocs </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">列為 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ESX </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">升級後另行手動的步驟）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">維持現版本</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TechDocs: Upgrade vSAN On-Disk Format Versions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S11-04</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Workload Domain &gt; Updates</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Precheck → </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">更新 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">vLCM image → ESX </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">升級（叢集 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">rolling</t>
     </r>
     <r>
       <rPr>
@@ -21592,90 +21709,6 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">TechDocs: About the vSAN Disk Format</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S11-04</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Workload Domain &gt; Updates</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Precheck → </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">更新 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">vLCM image → ESX </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">升級（叢集 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">rolling</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">VCF Ops / SDDC Manager &gt; Workload Domain &gt; Updates</t>
   </si>
   <si>
@@ -21921,16 +21954,35 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">vSAN format </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">升級後不可退</t>
+      <t xml:space="preserve">vSAN on-disk format </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">不升，主機退版不受 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">format </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">限制</t>
     </r>
   </si>
   <si>
@@ -23256,7 +23308,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Observation, vSAN Format &amp; Close-out</t>
+      <t xml:space="preserve">Observation &amp; Close-out</t>
     </r>
     <r>
       <rPr>
@@ -23266,7 +23318,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">｜觀察期、</t>
+      <t xml:space="preserve">｜觀察期與收尾｜</t>
     </r>
     <r>
       <rPr>
@@ -23277,7 +23329,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">vSAN on-disk format </t>
+      <t xml:space="preserve">G5 Gate</t>
     </r>
     <r>
       <rPr>
@@ -23287,7 +23339,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">與收尾｜</t>
+      <t xml:space="preserve">｜負責：</t>
     </r>
     <r>
       <rPr>
@@ -23298,7 +23350,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">G5 ⚠ PONR</t>
+      <t xml:space="preserve">PM</t>
     </r>
     <r>
       <rPr>
@@ -23308,7 +23360,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">｜負責：</t>
+      <t xml:space="preserve">、</t>
     </r>
     <r>
       <rPr>
@@ -23319,7 +23371,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">PM</t>
+      <t xml:space="preserve">ARC</t>
     </r>
     <r>
       <rPr>
@@ -23340,7 +23392,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">ARC</t>
+      <t xml:space="preserve">ENG</t>
     </r>
     <r>
       <rPr>
@@ -23361,27 +23413,6 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">ENG</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10.5"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10.5"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
       <t xml:space="preserve">SYS</t>
     </r>
   </si>
@@ -23408,6 +23439,15 @@
       </rPr>
       <t xml:space="preserve">G5</t>
     </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（結案）</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">簽核</t>
@@ -23433,11 +23473,86 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">升級（三個叢集；之後主機軟體無法退版）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Cluster &gt; vSAN &gt; Disk Management &gt; Upgrade</t>
+      <t xml:space="preserve">不升級（客戶決定，三個叢集維持現版本）：此為選擇性步驟，僅新版 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">format </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">才有的功能不啟用；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">vSAN Health </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">若出現 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">format </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">版本提示，列為已知項目</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">記錄於 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">As-Built</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">S16-03</t>
@@ -23666,35 +23781,31 @@
   <si>
     <r>
       <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFA6192E"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">vSAN format </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFA6192E"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">升級後無退版手段 → </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFA6192E"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">PONR</t>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本步無不可逆動作；日後若要升 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">vSAN on-disk format</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，另案評估（升級後無退版手段）</t>
     </r>
   </si>
   <si>
@@ -25653,13 +25764,37 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">G5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vSAN on-disk format</t>
-  </si>
-  <si>
-    <t xml:space="preserve">觀察期無重大事件、客戶簽核</t>
+    <t xml:space="preserve">結案</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">觀察期無重大事件、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">As-Built </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">交付、客戶簽核</t>
+    </r>
   </si>
   <si>
     <r>
@@ -28523,6 +28658,33 @@
   </si>
   <si>
     <t xml:space="preserve">https://interopmatrix.broadcom.com/Interoperability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vSAN</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Upgrade vSAN On-Disk Format Versions</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（本案不執行）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">https://techdocs.broadcom.com/us/en/vmware-cis/vcf/vcf-9-0-and-later/9-1/deployment/upgrading-cloud-foundation/upgrade-the-management-domain-to-vmware-cloud-foundation-5-2/upgrade-vsan-on-disk-format-versions.html</t>
   </si>
   <si>
     <t xml:space="preserve">Upgrade sequence and related issues for VCF and vSphere Foundation 9.1</t>
@@ -35422,7 +35584,7 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="11" t="s">
+      <c r="A22" s="9" t="s">
         <v>35</v>
       </c>
       <c r="B22" s="10" t="s">
@@ -35456,26 +35618,26 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="46" t="s">
-        <v>1055</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="47" t="s">
-        <v>1056</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>1057</v>
+        <v>1060</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>1058</v>
+        <v>1061</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>1059</v>
+        <v>1062</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>1060</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35483,13 +35645,13 @@
         <v>50</v>
       </c>
       <c r="B4" s="49" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>1062</v>
+        <v>1065</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>1063</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35497,13 +35659,13 @@
         <v>50</v>
       </c>
       <c r="B5" s="49" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>1064</v>
+        <v>1067</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>1065</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35511,27 +35673,27 @@
         <v>50</v>
       </c>
       <c r="B6" s="49" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>1066</v>
+        <v>1069</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>1067</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>1068</v>
+        <v>1071</v>
       </c>
       <c r="B7" s="49" t="s">
-        <v>1069</v>
+        <v>1072</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="41" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35539,13 +35701,13 @@
         <v>57</v>
       </c>
       <c r="B8" s="49" t="s">
-        <v>1072</v>
+        <v>1075</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>1073</v>
+        <v>1076</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>1074</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35553,13 +35715,13 @@
         <v>57</v>
       </c>
       <c r="B9" s="49" t="s">
-        <v>1072</v>
+        <v>1075</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>1075</v>
+        <v>1078</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>1076</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35567,13 +35729,13 @@
         <v>57</v>
       </c>
       <c r="B10" s="49" t="s">
-        <v>1077</v>
+        <v>1080</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>1078</v>
+        <v>1081</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>1079</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35581,13 +35743,13 @@
         <v>57</v>
       </c>
       <c r="B11" s="49" t="s">
-        <v>1080</v>
+        <v>1083</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>1081</v>
+        <v>1084</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>1082</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35595,13 +35757,13 @@
         <v>59</v>
       </c>
       <c r="B12" s="49" t="s">
-        <v>1083</v>
+        <v>1086</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>1084</v>
+        <v>1087</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>1085</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35609,13 +35771,13 @@
         <v>59</v>
       </c>
       <c r="B13" s="49" t="s">
-        <v>1083</v>
+        <v>1086</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>1086</v>
+        <v>1089</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>1087</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35623,13 +35785,13 @@
         <v>59</v>
       </c>
       <c r="B14" s="49" t="s">
-        <v>1083</v>
+        <v>1086</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>1088</v>
+        <v>1091</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>1089</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35637,41 +35799,41 @@
         <v>59</v>
       </c>
       <c r="B15" s="49" t="s">
-        <v>1090</v>
+        <v>1093</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>1091</v>
+        <v>1094</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>1092</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>1093</v>
+        <v>1096</v>
       </c>
       <c r="B16" s="49" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>1094</v>
+        <v>1097</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>1095</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B17" s="49" t="s">
         <v>1093</v>
       </c>
-      <c r="B17" s="49" t="s">
-        <v>1090</v>
-      </c>
       <c r="C17" s="12" t="s">
-        <v>1096</v>
+        <v>1099</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>1097</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35679,13 +35841,13 @@
         <v>63</v>
       </c>
       <c r="B18" s="49" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>1098</v>
+        <v>1101</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>1099</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35693,13 +35855,13 @@
         <v>63</v>
       </c>
       <c r="B19" s="49" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>1100</v>
+        <v>1103</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>1101</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35707,111 +35869,111 @@
         <v>63</v>
       </c>
       <c r="B20" s="49" t="s">
-        <v>1090</v>
+        <v>1093</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>1103</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>1027</v>
+        <v>1030</v>
       </c>
       <c r="B21" s="49" t="s">
-        <v>1083</v>
+        <v>1086</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>1104</v>
+        <v>1107</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>1027</v>
+        <v>1030</v>
       </c>
       <c r="B22" s="49" t="s">
-        <v>1083</v>
+        <v>1086</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>1106</v>
+        <v>1109</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>1107</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>1037</v>
+        <v>1040</v>
       </c>
       <c r="B23" s="49" t="s">
-        <v>1083</v>
+        <v>1086</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>1109</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>1037</v>
+        <v>1040</v>
       </c>
       <c r="B24" s="49" t="s">
-        <v>1090</v>
+        <v>1093</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>1110</v>
+        <v>1113</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>1111</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="B25" s="49" t="s">
-        <v>1083</v>
+        <v>1086</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>1112</v>
+        <v>1115</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>1113</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="B26" s="49" t="s">
-        <v>1114</v>
+        <v>1117</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>1115</v>
+        <v>1118</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>1116</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>1118</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35819,41 +35981,41 @@
         <v>53</v>
       </c>
       <c r="B28" s="49" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>1119</v>
+        <v>1122</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>1120</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="13" t="s">
-        <v>1121</v>
+        <v>1124</v>
       </c>
       <c r="B29" s="49" t="s">
-        <v>1090</v>
+        <v>1093</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>1123</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>1121</v>
+        <v>1124</v>
       </c>
       <c r="B30" s="49" t="s">
-        <v>1124</v>
+        <v>1127</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>1125</v>
+        <v>1128</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>1126</v>
+        <v>1129</v>
       </c>
     </row>
   </sheetData>
@@ -36546,7 +36708,7 @@
       <c r="C20" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="D20" s="16" t="s">
+      <c r="D20" s="14" t="s">
         <v>35</v>
       </c>
       <c r="E20" s="12" t="n">
@@ -42043,7 +42205,7 @@
       <c r="N150" s="26"/>
       <c r="O150" s="26"/>
     </row>
-    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="151" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="12" t="s">
         <v>72</v>
       </c>
@@ -42063,9 +42225,11 @@
         <v>620</v>
       </c>
       <c r="G151" s="24"/>
-      <c r="H151" s="12"/>
+      <c r="H151" s="13" t="s">
+        <v>621</v>
+      </c>
       <c r="I151" s="24" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="J151" s="12" t="s">
         <v>117</v>
@@ -42092,13 +42256,13 @@
         <v>167</v>
       </c>
       <c r="E152" s="12" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="F152" s="12" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="G152" s="24" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H152" s="12"/>
       <c r="I152" s="24" t="s">
@@ -42129,10 +42293,10 @@
         <v>172</v>
       </c>
       <c r="E153" s="12" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="F153" s="12" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="G153" s="24"/>
       <c r="H153" s="13" t="s">
@@ -42164,10 +42328,10 @@
         <v>172</v>
       </c>
       <c r="E154" s="12" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F154" s="12" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="G154" s="24"/>
       <c r="H154" s="13" t="s">
@@ -42175,7 +42339,7 @@
       </c>
       <c r="I154" s="24"/>
       <c r="J154" s="12" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="K154" s="25" t="s">
         <v>111</v>
@@ -42185,7 +42349,7 @@
       <c r="N154" s="26"/>
       <c r="O154" s="26"/>
     </row>
-    <row r="155" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="155" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="12" t="s">
         <v>72</v>
       </c>
@@ -42199,15 +42363,15 @@
         <v>177</v>
       </c>
       <c r="E155" s="12" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="F155" s="13" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="G155" s="24"/>
       <c r="H155" s="12"/>
       <c r="I155" s="24" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="J155" s="12" t="s">
         <v>127</v>
@@ -42225,7 +42389,7 @@
         <v>74</v>
       </c>
       <c r="B156" s="38" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C156" s="39" t="s">
         <v>76</v>
@@ -42235,7 +42399,7 @@
       </c>
       <c r="E156" s="38"/>
       <c r="F156" s="40" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="G156" s="38"/>
       <c r="H156" s="38"/>
@@ -42252,7 +42416,7 @@
         <v>74</v>
       </c>
       <c r="B157" s="12" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C157" s="13" t="s">
         <v>76</v>
@@ -42261,7 +42425,7 @@
         <v>104</v>
       </c>
       <c r="E157" s="12" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="F157" s="12" t="s">
         <v>513</v>
@@ -42289,7 +42453,7 @@
         <v>74</v>
       </c>
       <c r="B158" s="12" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C158" s="13" t="s">
         <v>76</v>
@@ -42298,10 +42462,10 @@
         <v>104</v>
       </c>
       <c r="E158" s="12" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="F158" s="13" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="G158" s="24"/>
       <c r="H158" s="13" t="s">
@@ -42326,7 +42490,7 @@
         <v>74</v>
       </c>
       <c r="B159" s="12" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C159" s="13" t="s">
         <v>76</v>
@@ -42335,10 +42499,10 @@
         <v>104</v>
       </c>
       <c r="E159" s="12" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="F159" s="12" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="G159" s="24"/>
       <c r="H159" s="13" t="s">
@@ -42361,7 +42525,7 @@
         <v>74</v>
       </c>
       <c r="B160" s="12" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C160" s="13" t="s">
         <v>76</v>
@@ -42370,7 +42534,7 @@
         <v>104</v>
       </c>
       <c r="E160" s="12" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="F160" s="12" t="s">
         <v>517</v>
@@ -42398,7 +42562,7 @@
         <v>74</v>
       </c>
       <c r="B161" s="12" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C161" s="13" t="s">
         <v>76</v>
@@ -42407,7 +42571,7 @@
         <v>104</v>
       </c>
       <c r="E161" s="12" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="F161" s="12" t="s">
         <v>520</v>
@@ -42433,7 +42597,7 @@
         <v>74</v>
       </c>
       <c r="B162" s="12" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C162" s="13" t="s">
         <v>76</v>
@@ -42442,7 +42606,7 @@
         <v>104</v>
       </c>
       <c r="E162" s="12" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="F162" s="13" t="s">
         <v>523</v>
@@ -42472,7 +42636,7 @@
         <v>74</v>
       </c>
       <c r="B163" s="12" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C163" s="13" t="s">
         <v>76</v>
@@ -42481,7 +42645,7 @@
         <v>104</v>
       </c>
       <c r="E163" s="12" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="F163" s="13" t="s">
         <v>527</v>
@@ -42507,7 +42671,7 @@
         <v>74</v>
       </c>
       <c r="B164" s="12" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C164" s="13" t="s">
         <v>76</v>
@@ -42516,7 +42680,7 @@
         <v>104</v>
       </c>
       <c r="E164" s="12" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="F164" s="12" t="s">
         <v>529</v>
@@ -42546,7 +42710,7 @@
         <v>74</v>
       </c>
       <c r="B165" s="12" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C165" s="13" t="s">
         <v>76</v>
@@ -42555,7 +42719,7 @@
         <v>104</v>
       </c>
       <c r="E165" s="12" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="F165" s="13" t="s">
         <v>534</v>
@@ -42581,7 +42745,7 @@
         <v>74</v>
       </c>
       <c r="B166" s="12" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C166" s="13" t="s">
         <v>76</v>
@@ -42590,7 +42754,7 @@
         <v>167</v>
       </c>
       <c r="E166" s="12" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="F166" s="12" t="s">
         <v>536</v>
@@ -42620,7 +42784,7 @@
         <v>74</v>
       </c>
       <c r="B167" s="12" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C167" s="13" t="s">
         <v>76</v>
@@ -42629,7 +42793,7 @@
         <v>167</v>
       </c>
       <c r="E167" s="12" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="F167" s="13" t="s">
         <v>540</v>
@@ -42655,7 +42819,7 @@
         <v>74</v>
       </c>
       <c r="B168" s="12" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C168" s="13" t="s">
         <v>76</v>
@@ -42664,7 +42828,7 @@
         <v>172</v>
       </c>
       <c r="E168" s="12" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="F168" s="13" t="s">
         <v>542</v>
@@ -42692,7 +42856,7 @@
         <v>74</v>
       </c>
       <c r="B169" s="12" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C169" s="13" t="s">
         <v>76</v>
@@ -42701,7 +42865,7 @@
         <v>177</v>
       </c>
       <c r="E169" s="12" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="F169" s="12" t="s">
         <v>545</v>
@@ -42727,7 +42891,7 @@
         <v>74</v>
       </c>
       <c r="B170" s="12" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C170" s="13" t="s">
         <v>76</v>
@@ -42736,7 +42900,7 @@
         <v>177</v>
       </c>
       <c r="E170" s="12" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="F170" s="12" t="s">
         <v>548</v>
@@ -42762,7 +42926,7 @@
         <v>77</v>
       </c>
       <c r="B171" s="38" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C171" s="39" t="s">
         <v>76</v>
@@ -42772,7 +42936,7 @@
       </c>
       <c r="E171" s="38"/>
       <c r="F171" s="40" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="G171" s="38"/>
       <c r="H171" s="38"/>
@@ -42789,7 +42953,7 @@
         <v>77</v>
       </c>
       <c r="B172" s="12" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C172" s="13" t="s">
         <v>76</v>
@@ -42798,7 +42962,7 @@
         <v>104</v>
       </c>
       <c r="E172" s="12" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="F172" s="13" t="s">
         <v>552</v>
@@ -42822,7 +42986,7 @@
         <v>77</v>
       </c>
       <c r="B173" s="12" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C173" s="13" t="s">
         <v>76</v>
@@ -42831,7 +42995,7 @@
         <v>104</v>
       </c>
       <c r="E173" s="12" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="F173" s="12" t="s">
         <v>554</v>
@@ -42861,7 +43025,7 @@
         <v>77</v>
       </c>
       <c r="B174" s="12" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C174" s="13" t="s">
         <v>76</v>
@@ -42870,7 +43034,7 @@
         <v>167</v>
       </c>
       <c r="E174" s="12" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="F174" s="13" t="s">
         <v>559</v>
@@ -42900,7 +43064,7 @@
         <v>77</v>
       </c>
       <c r="B175" s="12" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C175" s="13" t="s">
         <v>76</v>
@@ -42909,7 +43073,7 @@
         <v>167</v>
       </c>
       <c r="E175" s="12" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="F175" s="12" t="s">
         <v>563</v>
@@ -42939,7 +43103,7 @@
         <v>77</v>
       </c>
       <c r="B176" s="12" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C176" s="13" t="s">
         <v>76</v>
@@ -42948,7 +43112,7 @@
         <v>167</v>
       </c>
       <c r="E176" s="12" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="F176" s="13" t="s">
         <v>567</v>
@@ -42976,7 +43140,7 @@
         <v>77</v>
       </c>
       <c r="B177" s="12" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C177" s="13" t="s">
         <v>76</v>
@@ -42985,7 +43149,7 @@
         <v>172</v>
       </c>
       <c r="E177" s="12" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="F177" s="12" t="s">
         <v>571</v>
@@ -43013,7 +43177,7 @@
         <v>77</v>
       </c>
       <c r="B178" s="12" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C178" s="13" t="s">
         <v>76</v>
@@ -43022,10 +43186,10 @@
         <v>172</v>
       </c>
       <c r="E178" s="12" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="F178" s="12" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="G178" s="24" t="s">
         <v>574</v>
@@ -43050,7 +43214,7 @@
         <v>77</v>
       </c>
       <c r="B179" s="12" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C179" s="13" t="s">
         <v>76</v>
@@ -43059,7 +43223,7 @@
         <v>172</v>
       </c>
       <c r="E179" s="12" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="F179" s="12" t="s">
         <v>573</v>
@@ -43087,7 +43251,7 @@
         <v>77</v>
       </c>
       <c r="B180" s="12" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C180" s="13" t="s">
         <v>76</v>
@@ -43096,7 +43260,7 @@
         <v>177</v>
       </c>
       <c r="E180" s="12" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="F180" s="12" t="s">
         <v>577</v>
@@ -43122,7 +43286,7 @@
         <v>79</v>
       </c>
       <c r="B181" s="38" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C181" s="39" t="s">
         <v>76</v>
@@ -43132,7 +43296,7 @@
       </c>
       <c r="E181" s="38"/>
       <c r="F181" s="40" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="G181" s="38"/>
       <c r="H181" s="38"/>
@@ -43149,7 +43313,7 @@
         <v>79</v>
       </c>
       <c r="B182" s="12" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C182" s="13" t="s">
         <v>76</v>
@@ -43158,7 +43322,7 @@
         <v>104</v>
       </c>
       <c r="E182" s="12" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="F182" s="12" t="s">
         <v>582</v>
@@ -43186,7 +43350,7 @@
         <v>79</v>
       </c>
       <c r="B183" s="12" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C183" s="13" t="s">
         <v>76</v>
@@ -43195,7 +43359,7 @@
         <v>104</v>
       </c>
       <c r="E183" s="12" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="F183" s="12" t="s">
         <v>585</v>
@@ -43223,7 +43387,7 @@
         <v>79</v>
       </c>
       <c r="B184" s="12" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C184" s="13" t="s">
         <v>76</v>
@@ -43232,7 +43396,7 @@
         <v>104</v>
       </c>
       <c r="E184" s="12" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="F184" s="13" t="s">
         <v>588</v>
@@ -43262,7 +43426,7 @@
         <v>79</v>
       </c>
       <c r="B185" s="12" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C185" s="13" t="s">
         <v>76</v>
@@ -43271,7 +43435,7 @@
         <v>104</v>
       </c>
       <c r="E185" s="12" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="F185" s="12" t="s">
         <v>592</v>
@@ -43297,7 +43461,7 @@
         <v>79</v>
       </c>
       <c r="B186" s="12" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C186" s="13" t="s">
         <v>76</v>
@@ -43306,7 +43470,7 @@
         <v>167</v>
       </c>
       <c r="E186" s="12" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="F186" s="12" t="s">
         <v>595</v>
@@ -43336,7 +43500,7 @@
         <v>79</v>
       </c>
       <c r="B187" s="12" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C187" s="13" t="s">
         <v>76</v>
@@ -43345,7 +43509,7 @@
         <v>167</v>
       </c>
       <c r="E187" s="12" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="F187" s="12" t="s">
         <v>599</v>
@@ -43371,7 +43535,7 @@
         <v>79</v>
       </c>
       <c r="B188" s="12" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C188" s="13" t="s">
         <v>76</v>
@@ -43380,7 +43544,7 @@
         <v>172</v>
       </c>
       <c r="E188" s="12" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="F188" s="12" t="s">
         <v>602</v>
@@ -43410,7 +43574,7 @@
         <v>79</v>
       </c>
       <c r="B189" s="12" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C189" s="13" t="s">
         <v>76</v>
@@ -43419,7 +43583,7 @@
         <v>172</v>
       </c>
       <c r="E189" s="12" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F189" s="12" t="s">
         <v>605</v>
@@ -43445,7 +43609,7 @@
         <v>79</v>
       </c>
       <c r="B190" s="12" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C190" s="13" t="s">
         <v>76</v>
@@ -43454,7 +43618,7 @@
         <v>177</v>
       </c>
       <c r="E190" s="12" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F190" s="34" t="s">
         <v>607</v>
@@ -43480,7 +43644,7 @@
         <v>81</v>
       </c>
       <c r="B191" s="38" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C191" s="39" t="s">
         <v>76</v>
@@ -43490,7 +43654,7 @@
       </c>
       <c r="E191" s="38"/>
       <c r="F191" s="40" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="G191" s="38"/>
       <c r="H191" s="38"/>
@@ -43507,7 +43671,7 @@
         <v>81</v>
       </c>
       <c r="B192" s="12" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C192" s="13" t="s">
         <v>76</v>
@@ -43516,7 +43680,7 @@
         <v>104</v>
       </c>
       <c r="E192" s="12" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="F192" s="12" t="s">
         <v>613</v>
@@ -43542,7 +43706,7 @@
         <v>81</v>
       </c>
       <c r="B193" s="12" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C193" s="13" t="s">
         <v>76</v>
@@ -43551,7 +43715,7 @@
         <v>104</v>
       </c>
       <c r="E193" s="12" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="F193" s="12" t="s">
         <v>616</v>
@@ -43574,12 +43738,12 @@
       <c r="N193" s="26"/>
       <c r="O193" s="26"/>
     </row>
-    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="194" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="12" t="s">
         <v>81</v>
       </c>
       <c r="B194" s="12" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C194" s="13" t="s">
         <v>76</v>
@@ -43588,15 +43752,17 @@
         <v>104</v>
       </c>
       <c r="E194" s="12" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="F194" s="12" t="s">
         <v>620</v>
       </c>
       <c r="G194" s="24"/>
-      <c r="H194" s="12"/>
+      <c r="H194" s="13" t="s">
+        <v>621</v>
+      </c>
       <c r="I194" s="24" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="J194" s="12" t="s">
         <v>117</v>
@@ -43614,7 +43780,7 @@
         <v>81</v>
       </c>
       <c r="B195" s="12" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C195" s="13" t="s">
         <v>76</v>
@@ -43623,13 +43789,13 @@
         <v>167</v>
       </c>
       <c r="E195" s="12" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="F195" s="12" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="G195" s="24" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H195" s="12"/>
       <c r="I195" s="24" t="s">
@@ -43651,7 +43817,7 @@
         <v>81</v>
       </c>
       <c r="B196" s="12" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C196" s="13" t="s">
         <v>76</v>
@@ -43660,10 +43826,10 @@
         <v>172</v>
       </c>
       <c r="E196" s="12" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="F196" s="12" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="G196" s="24"/>
       <c r="H196" s="13" t="s">
@@ -43686,7 +43852,7 @@
         <v>81</v>
       </c>
       <c r="B197" s="12" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C197" s="13" t="s">
         <v>76</v>
@@ -43695,10 +43861,10 @@
         <v>172</v>
       </c>
       <c r="E197" s="12" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="F197" s="12" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="G197" s="24"/>
       <c r="H197" s="13" t="s">
@@ -43706,7 +43872,7 @@
       </c>
       <c r="I197" s="24"/>
       <c r="J197" s="12" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="K197" s="25" t="s">
         <v>111</v>
@@ -43716,12 +43882,12 @@
       <c r="N197" s="26"/>
       <c r="O197" s="26"/>
     </row>
-    <row r="198" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="198" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="12" t="s">
         <v>81</v>
       </c>
       <c r="B198" s="12" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C198" s="13" t="s">
         <v>76</v>
@@ -43730,15 +43896,15 @@
         <v>177</v>
       </c>
       <c r="E198" s="12" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="F198" s="13" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="G198" s="24"/>
       <c r="H198" s="12"/>
       <c r="I198" s="24" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="J198" s="12" t="s">
         <v>127</v>
@@ -43766,7 +43932,7 @@
       </c>
       <c r="E199" s="41"/>
       <c r="F199" s="43" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="G199" s="41"/>
       <c r="H199" s="41"/>
@@ -43792,14 +43958,14 @@
         <v>104</v>
       </c>
       <c r="E200" s="12" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="F200" s="13" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="G200" s="24"/>
       <c r="H200" s="13" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="I200" s="24"/>
       <c r="J200" s="12" t="s">
@@ -43813,7 +43979,7 @@
       <c r="N200" s="26"/>
       <c r="O200" s="26"/>
     </row>
-    <row r="201" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="201" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="12" t="s">
         <v>83</v>
       </c>
@@ -43827,22 +43993,20 @@
         <v>167</v>
       </c>
       <c r="E201" s="12" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="F201" s="12" t="s">
-        <v>690</v>
-      </c>
-      <c r="G201" s="24" t="s">
         <v>691</v>
       </c>
+      <c r="G201" s="24"/>
       <c r="H201" s="13" t="s">
-        <v>42</v>
+        <v>692</v>
       </c>
       <c r="I201" s="24" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="J201" s="12" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="K201" s="25" t="s">
         <v>111</v>
@@ -43866,10 +44030,10 @@
         <v>167</v>
       </c>
       <c r="E202" s="12" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="F202" s="12" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="G202" s="24"/>
       <c r="H202" s="12"/>
@@ -43899,15 +44063,15 @@
         <v>167</v>
       </c>
       <c r="E203" s="12" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="F203" s="12" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="G203" s="24"/>
       <c r="H203" s="12"/>
       <c r="I203" s="24" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="J203" s="12" t="s">
         <v>117</v>
@@ -43934,14 +44098,14 @@
         <v>172</v>
       </c>
       <c r="E204" s="12" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="F204" s="13" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="G204" s="24"/>
       <c r="H204" s="13" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="I204" s="24"/>
       <c r="J204" s="12" t="s">
@@ -43969,15 +44133,15 @@
         <v>177</v>
       </c>
       <c r="E205" s="12" t="s">
-        <v>700</v>
-      </c>
-      <c r="F205" s="16" t="s">
         <v>701</v>
+      </c>
+      <c r="F205" s="13" t="s">
+        <v>702</v>
       </c>
       <c r="G205" s="24"/>
       <c r="H205" s="12"/>
       <c r="I205" s="24" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="J205" s="12" t="s">
         <v>176</v>
@@ -44041,49 +44205,49 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>95</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C4" s="44" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="F4" s="12" t="s">
         <v>50</v>
@@ -44091,19 +44255,19 @@
     </row>
     <row r="5" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C5" s="45" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="F5" s="12" t="s">
         <v>53</v>
@@ -44111,19 +44275,19 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C6" s="45" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="F6" s="12" t="s">
         <v>55</v>
@@ -44131,19 +44295,19 @@
     </row>
     <row r="7" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="F7" s="12" t="s">
         <v>57</v>
@@ -44151,19 +44315,19 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C8" s="45" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="F8" s="12" t="s">
         <v>59</v>
@@ -44171,19 +44335,19 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C9" s="45" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="F9" s="12" t="s">
         <v>61</v>
@@ -44191,19 +44355,19 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C10" s="45" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="F10" s="12" t="s">
         <v>63</v>
@@ -44211,19 +44375,19 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="C11" s="44" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F11" s="12" t="s">
         <v>70</v>
@@ -44231,19 +44395,19 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
+        <v>745</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>746</v>
+      </c>
+      <c r="C12" s="44" t="s">
+        <v>712</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>747</v>
+      </c>
+      <c r="E12" s="12" t="s">
         <v>744</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>745</v>
-      </c>
-      <c r="C12" s="44" t="s">
-        <v>711</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>746</v>
-      </c>
-      <c r="E12" s="12" t="s">
-        <v>743</v>
       </c>
       <c r="F12" s="12" t="s">
         <v>79</v>
@@ -44251,36 +44415,36 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="C13" s="44" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="C14" s="45" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="E14" s="12" t="s">
         <v>561</v>
@@ -44291,36 +44455,36 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C15" s="44" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C16" s="45" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E16" s="12" t="s">
         <v>561</v>
@@ -44362,12 +44526,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="46" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="47" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -44375,28 +44539,28 @@
         <v>23</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="J3" s="8" t="s">
         <v>101</v>
@@ -44407,19 +44571,19 @@
         <v>25</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="G4" s="26"/>
       <c r="H4" s="26"/>
@@ -44428,22 +44592,22 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="F5" s="34" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="G5" s="26"/>
       <c r="H5" s="26"/>
@@ -44455,19 +44619,19 @@
         <v>29</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="G6" s="26"/>
       <c r="H6" s="26"/>
@@ -44476,22 +44640,22 @@
     </row>
     <row r="7" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B7" s="12" t="s">
         <v>70</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="F7" s="34" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="G7" s="26"/>
       <c r="H7" s="26"/>
@@ -44500,22 +44664,22 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B8" s="12" t="s">
         <v>79</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="F8" s="34" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="G8" s="26"/>
       <c r="H8" s="26"/>
@@ -44524,12 +44688,12 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>794</v>
+        <v>35</v>
       </c>
       <c r="B9" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="13" t="s">
         <v>795</v>
       </c>
       <c r="D9" s="13" t="s">
@@ -44538,8 +44702,8 @@
       <c r="E9" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="F9" s="34" t="s">
-        <v>782</v>
+      <c r="F9" s="13" t="s">
+        <v>778</v>
       </c>
       <c r="G9" s="26"/>
       <c r="H9" s="26"/>
@@ -44630,10 +44794,10 @@
         <v>807</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="D4" s="12" t="s">
         <v>808</v>
@@ -44654,10 +44818,10 @@
         <v>810</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="D5" s="12" t="s">
         <v>808</v>
@@ -44724,10 +44888,10 @@
         <v>819</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="D8" s="12" t="s">
         <v>808</v>
@@ -44746,7 +44910,7 @@
         <v>820</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>821</v>
@@ -44770,10 +44934,10 @@
         <v>823</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="D10" s="12" t="s">
         <v>808</v>
@@ -44840,7 +45004,7 @@
         <v>833</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C13" s="13" t="s">
         <v>834</v>
@@ -44864,7 +45028,7 @@
         <v>837</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C14" s="13" t="s">
         <v>834</v>
@@ -44888,10 +45052,10 @@
         <v>839</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="D15" s="12" t="s">
         <v>808</v>
@@ -44969,7 +45133,7 @@
         <v>845</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45267,7 +45431,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:C47"/>
+  <dimension ref="A1:C48"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -45329,7 +45493,7 @@
         <v>895</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C7" s="48" t="s">
         <v>896</v>
@@ -45373,7 +45537,7 @@
         <v>901</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C11" s="48" t="s">
         <v>904</v>
@@ -45406,7 +45570,7 @@
         <v>909</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="C14" s="48" t="s">
         <v>910</v>
@@ -45546,18 +45710,18 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>822</v>
+        <v>941</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="C27" s="48" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>943</v>
+        <v>822</v>
       </c>
       <c r="B28" s="12" t="s">
         <v>944</v>
@@ -45568,29 +45732,29 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>416</v>
+        <v>946</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="C29" s="48" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>142</v>
+        <v>416</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="C30" s="48" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>950</v>
+        <v>142</v>
       </c>
       <c r="B31" s="12" t="s">
         <v>951</v>
@@ -45614,7 +45778,7 @@
       <c r="A33" s="12" t="s">
         <v>956</v>
       </c>
-      <c r="B33" s="13" t="s">
+      <c r="B33" s="12" t="s">
         <v>957</v>
       </c>
       <c r="C33" s="48" t="s">
@@ -45625,7 +45789,7 @@
       <c r="A34" s="12" t="s">
         <v>959</v>
       </c>
-      <c r="B34" s="12" t="s">
+      <c r="B34" s="13" t="s">
         <v>960</v>
       </c>
       <c r="C34" s="48" t="s">
@@ -45689,20 +45853,20 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="12" t="s">
-        <v>506</v>
+        <v>977</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="C40" s="48" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="12" t="s">
-        <v>979</v>
-      </c>
-      <c r="B41" s="13" t="s">
+        <v>506</v>
+      </c>
+      <c r="B41" s="12" t="s">
         <v>980</v>
       </c>
       <c r="C41" s="48" t="s">
@@ -45711,40 +45875,40 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="12" t="s">
-        <v>203</v>
-      </c>
-      <c r="B42" s="12" t="s">
         <v>982</v>
       </c>
+      <c r="B42" s="13" t="s">
+        <v>983</v>
+      </c>
       <c r="C42" s="48" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="12" t="s">
-        <v>561</v>
+        <v>203</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="C43" s="48" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="12" t="s">
-        <v>578</v>
+        <v>561</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="C44" s="48" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="12" t="s">
-        <v>988</v>
+        <v>578</v>
       </c>
       <c r="B45" s="12" t="s">
         <v>989</v>
@@ -45766,13 +45930,24 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="12" t="s">
-        <v>632</v>
+        <v>994</v>
       </c>
       <c r="B47" s="12" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="C47" s="48" t="s">
-        <v>995</v>
+        <v>996</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="12" t="s">
+        <v>633</v>
+      </c>
+      <c r="B48" s="12" t="s">
+        <v>997</v>
+      </c>
+      <c r="C48" s="48" t="s">
+        <v>998</v>
       </c>
     </row>
   </sheetData>
@@ -45800,27 +45975,28 @@
     <hyperlink ref="C24" r:id="rId21" display="https://techdocs.broadcom.com/us/en/vmware-cis/vcf/vcf-9-0-and-later/9-1/release-notes/vmware-cloud-foundation-9-1-1-0-release-notes.html"/>
     <hyperlink ref="C25" r:id="rId22" display="https://techdocs.broadcom.com/us/en/vmware-cis/vcf/vcf-9-0-and-later/9-1/release-notes/vmware-cloud-foundation-9-1-1-0-release-notes/vmware-cloud-foundation-9-1-1-0-bill-of-material.html"/>
     <hyperlink ref="C26" r:id="rId23" display="https://interopmatrix.broadcom.com/Interoperability"/>
-    <hyperlink ref="C27" r:id="rId24" display="https://knowledge.broadcom.com/external/article/440630"/>
-    <hyperlink ref="C28" r:id="rId25" display="https://knowledge.broadcom.com/external/article/450972"/>
-    <hyperlink ref="C29" r:id="rId26" display="https://knowledge.broadcom.com/external/article/448258"/>
-    <hyperlink ref="C30" r:id="rId27" display="https://knowledge.broadcom.com/external/article/453612"/>
-    <hyperlink ref="C31" r:id="rId28" display="https://knowledge.broadcom.com/external/article/425102"/>
-    <hyperlink ref="C32" r:id="rId29" display="https://knowledge.broadcom.com/external/article/436924"/>
-    <hyperlink ref="C33" r:id="rId30" display="https://knowledge.broadcom.com/external/article/430524"/>
-    <hyperlink ref="C34" r:id="rId31" display="https://knowledge.broadcom.com/external/article/429205"/>
-    <hyperlink ref="C35" r:id="rId32" display="https://knowledge.broadcom.com/external/article/425169"/>
-    <hyperlink ref="C36" r:id="rId33" display="https://knowledge.broadcom.com/external/article/425489"/>
-    <hyperlink ref="C37" r:id="rId34" display="https://knowledge.broadcom.com/external/article/389563"/>
-    <hyperlink ref="C38" r:id="rId35" display="https://knowledge.broadcom.com/external/article/447667"/>
-    <hyperlink ref="C39" r:id="rId36" display="https://knowledge.broadcom.com/external/article/450345"/>
-    <hyperlink ref="C40" r:id="rId37" display="https://knowledge.broadcom.com/external/article/441333"/>
-    <hyperlink ref="C41" r:id="rId38" display="https://knowledge.broadcom.com/external/article/318582"/>
-    <hyperlink ref="C42" r:id="rId39" display="https://knowledge.broadcom.com/external/article/447218"/>
-    <hyperlink ref="C43" r:id="rId40" display="https://knowledge.broadcom.com/external/article/446701"/>
-    <hyperlink ref="C44" r:id="rId41" display="https://knowledge.broadcom.com/external/article/448322"/>
-    <hyperlink ref="C45" r:id="rId42" display="https://knowledge.broadcom.com/external/article/367383"/>
-    <hyperlink ref="C46" r:id="rId43" display="https://knowledge.broadcom.com/external/article/396777"/>
-    <hyperlink ref="C47" r:id="rId44" display="https://knowledge.broadcom.com/external/article/316592"/>
+    <hyperlink ref="C27" r:id="rId24" display="https://techdocs.broadcom.com/us/en/vmware-cis/vcf/vcf-9-0-and-later/9-1/deployment/upgrading-cloud-foundation/upgrade-the-management-domain-to-vmware-cloud-foundation-5-2/upgrade-vsan-on-disk-format-versions.html"/>
+    <hyperlink ref="C28" r:id="rId25" display="https://knowledge.broadcom.com/external/article/440630"/>
+    <hyperlink ref="C29" r:id="rId26" display="https://knowledge.broadcom.com/external/article/450972"/>
+    <hyperlink ref="C30" r:id="rId27" display="https://knowledge.broadcom.com/external/article/448258"/>
+    <hyperlink ref="C31" r:id="rId28" display="https://knowledge.broadcom.com/external/article/453612"/>
+    <hyperlink ref="C32" r:id="rId29" display="https://knowledge.broadcom.com/external/article/425102"/>
+    <hyperlink ref="C33" r:id="rId30" display="https://knowledge.broadcom.com/external/article/436924"/>
+    <hyperlink ref="C34" r:id="rId31" display="https://knowledge.broadcom.com/external/article/430524"/>
+    <hyperlink ref="C35" r:id="rId32" display="https://knowledge.broadcom.com/external/article/429205"/>
+    <hyperlink ref="C36" r:id="rId33" display="https://knowledge.broadcom.com/external/article/425169"/>
+    <hyperlink ref="C37" r:id="rId34" display="https://knowledge.broadcom.com/external/article/425489"/>
+    <hyperlink ref="C38" r:id="rId35" display="https://knowledge.broadcom.com/external/article/389563"/>
+    <hyperlink ref="C39" r:id="rId36" display="https://knowledge.broadcom.com/external/article/447667"/>
+    <hyperlink ref="C40" r:id="rId37" display="https://knowledge.broadcom.com/external/article/450345"/>
+    <hyperlink ref="C41" r:id="rId38" display="https://knowledge.broadcom.com/external/article/441333"/>
+    <hyperlink ref="C42" r:id="rId39" display="https://knowledge.broadcom.com/external/article/318582"/>
+    <hyperlink ref="C43" r:id="rId40" display="https://knowledge.broadcom.com/external/article/447218"/>
+    <hyperlink ref="C44" r:id="rId41" display="https://knowledge.broadcom.com/external/article/446701"/>
+    <hyperlink ref="C45" r:id="rId42" display="https://knowledge.broadcom.com/external/article/448322"/>
+    <hyperlink ref="C46" r:id="rId43" display="https://knowledge.broadcom.com/external/article/367383"/>
+    <hyperlink ref="C47" r:id="rId44" display="https://knowledge.broadcom.com/external/article/396777"/>
+    <hyperlink ref="C48" r:id="rId45" display="https://knowledge.broadcom.com/external/article/316592"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -45851,12 +46027,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="46" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>997</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -45864,22 +46040,22 @@
         <v>39</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>97</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>998</v>
+        <v>1001</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>1000</v>
+        <v>1003</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45887,45 +46063,45 @@
         <v>50</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>1002</v>
+        <v>1005</v>
       </c>
       <c r="C4" s="45" t="s">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>1004</v>
+        <v>1007</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>1008</v>
+        <v>1011</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>1009</v>
+        <v>1012</v>
       </c>
       <c r="C5" s="45" t="s">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>1010</v>
+        <v>1013</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>1013</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45933,22 +46109,22 @@
         <v>59</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="C6" s="45" t="s">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>1015</v>
+        <v>1018</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>1016</v>
+        <v>1019</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>1017</v>
+        <v>1020</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>1018</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45956,22 +46132,22 @@
         <v>61</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>1019</v>
+        <v>1022</v>
       </c>
       <c r="C7" s="45" t="s">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>1020</v>
+        <v>1023</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>1021</v>
+        <v>1024</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>1022</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45979,114 +46155,114 @@
         <v>63</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>1023</v>
+        <v>1026</v>
       </c>
       <c r="C8" s="45" t="s">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>1024</v>
+        <v>1027</v>
       </c>
       <c r="E8" s="12" t="s">
+        <v>1028</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>1029</v>
+      </c>
+      <c r="G8" s="12" t="s">
         <v>1025</v>
-      </c>
-      <c r="F8" s="12" t="s">
-        <v>1026</v>
-      </c>
-      <c r="G8" s="12" t="s">
-        <v>1022</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>1027</v>
+        <v>1030</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>1028</v>
+        <v>1031</v>
       </c>
       <c r="C9" s="45" t="s">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>1029</v>
+        <v>1032</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>1030</v>
+        <v>1033</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>1032</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>1034</v>
+        <v>1037</v>
       </c>
       <c r="C10" s="34" t="s">
-        <v>1035</v>
+        <v>1038</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>1037</v>
+        <v>1040</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>1038</v>
+        <v>1041</v>
       </c>
       <c r="C11" s="45" t="s">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>1039</v>
+        <v>1042</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
       <c r="C12" s="34" t="s">
-        <v>1035</v>
+        <v>1038</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>1045</v>
+        <v>1048</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>1046</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46094,45 +46270,45 @@
         <v>53</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>1047</v>
+        <v>1050</v>
       </c>
       <c r="C13" s="45" t="s">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>1048</v>
+        <v>1051</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>1049</v>
+        <v>1052</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>1050</v>
+        <v>1053</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>1051</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>1052</v>
+        <v>1055</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>1053</v>
+        <v>1056</v>
       </c>
       <c r="C14" s="34" t="s">
-        <v>1035</v>
+        <v>1038</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>1054</v>
+        <v>1057</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
     </row>
   </sheetData>
